--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="287">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,10 +505,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -3923,7 +3926,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -3953,8 +3956,12 @@
       <c r="K27" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="L27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4024,10 +4031,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4041,7 +4048,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4050,13 +4057,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4107,7 +4114,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4127,10 +4134,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4226,12 +4233,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4241,13 +4248,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4260,7 +4267,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4272,7 +4279,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4311,7 +4318,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4329,28 +4336,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4363,7 +4370,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4375,7 +4382,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4414,7 +4421,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4434,17 +4441,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4466,7 +4473,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4478,7 +4485,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4517,7 +4524,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4537,17 +4544,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4569,7 +4576,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4620,7 +4627,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4638,28 +4645,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4672,7 +4679,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4684,7 +4691,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4723,7 +4730,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4743,10 +4750,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4769,11 +4776,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4824,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4844,10 +4851,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4874,7 +4881,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4925,7 +4932,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4945,17 +4952,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4973,11 +4980,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5028,7 +5035,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5048,17 +5055,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5076,11 +5083,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5131,7 +5138,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5151,17 +5158,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5179,11 +5186,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5234,7 +5241,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5254,10 +5261,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5271,7 +5278,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5280,13 +5287,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5337,7 +5344,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5357,10 +5364,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5374,7 +5381,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5383,13 +5390,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5440,7 +5447,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5460,10 +5467,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5486,7 +5493,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5539,7 +5546,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5559,10 +5566,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5618,25 +5625,25 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5656,10 +5663,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5682,7 +5689,7 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -5735,7 +5742,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5755,10 +5762,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5781,7 +5788,7 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -5834,7 +5841,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5854,10 +5861,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5880,7 +5887,7 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -5933,7 +5940,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5953,10 +5960,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5970,7 +5977,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -5979,10 +5986,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6034,7 +6041,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6054,10 +6061,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6155,10 +6162,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6256,10 +6263,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6357,10 +6364,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6458,10 +6465,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6561,10 +6568,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6664,10 +6671,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6767,10 +6774,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6870,10 +6877,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6971,10 +6978,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7004,7 +7011,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
@@ -7030,7 +7037,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7048,7 +7055,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7068,10 +7075,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7105,7 +7112,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>74</v>
@@ -7147,7 +7154,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7167,10 +7174,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7193,7 +7200,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7246,7 +7253,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7266,10 +7273,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7292,7 +7299,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7345,7 +7352,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7365,10 +7372,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7391,7 +7398,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7444,7 +7451,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7464,10 +7471,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7490,7 +7497,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7543,7 +7550,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7563,10 +7570,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7589,7 +7596,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7642,7 +7649,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7662,10 +7669,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7688,7 +7695,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7741,7 +7748,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7761,10 +7768,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7787,7 +7794,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7840,7 +7847,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7860,10 +7867,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7886,7 +7893,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7939,7 +7946,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -7959,10 +7966,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7985,7 +7992,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8038,7 +8045,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8058,10 +8065,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8084,7 +8091,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8137,7 +8144,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8157,10 +8164,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8258,10 +8265,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8359,10 +8366,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8460,10 +8467,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8561,10 +8568,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8664,10 +8671,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8767,10 +8774,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8870,10 +8877,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8973,10 +8980,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9074,10 +9081,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9104,7 +9111,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9113,7 +9120,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>74</v>
@@ -9155,7 +9162,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9175,10 +9182,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9212,7 +9219,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>74</v>
@@ -9254,7 +9261,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9274,10 +9281,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9300,7 +9307,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9353,7 +9360,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements-a-la-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
